--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_21-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_21-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15CC113-6044-4EC6-BAB3-0FDC4138EDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A6DC96-D4B8-4B10-AECC-41510239C661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33960" yWindow="255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="3945" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="257">
   <si>
     <t>SKU</t>
   </si>
@@ -724,45 +724,6 @@
     <t>£15.25</t>
   </si>
   <si>
-    <t>£18.10</t>
-  </si>
-  <si>
-    <t>£22.39</t>
-  </si>
-  <si>
-    <t>£23.42</t>
-  </si>
-  <si>
-    <t>£30.08</t>
-  </si>
-  <si>
-    <t>£32.99</t>
-  </si>
-  <si>
-    <t>£36.74</t>
-  </si>
-  <si>
-    <t>£40.42</t>
-  </si>
-  <si>
-    <t>£39.91</t>
-  </si>
-  <si>
-    <t>£49.15</t>
-  </si>
-  <si>
-    <t>£49.61</t>
-  </si>
-  <si>
-    <t>£59.61</t>
-  </si>
-  <si>
-    <t>£60.64</t>
-  </si>
-  <si>
-    <t>£59.79</t>
-  </si>
-  <si>
     <t>£91.99</t>
   </si>
   <si>
@@ -806,6 +767,30 @@
   </si>
   <si>
     <t>£711.4</t>
+  </si>
+  <si>
+    <t>£21.95</t>
+  </si>
+  <si>
+    <t>£29.80</t>
+  </si>
+  <si>
+    <t>£32.65</t>
+  </si>
+  <si>
+    <t>£40.15</t>
+  </si>
+  <si>
+    <t>£48.85</t>
+  </si>
+  <si>
+    <t>£49.35</t>
+  </si>
+  <si>
+    <t>£59.35</t>
+  </si>
+  <si>
+    <t>£59.45</t>
   </si>
 </sst>
 </file>
@@ -1324,10 +1309,10 @@
         <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="O3" t="s">
-        <v>234</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
         <v>28</v>
@@ -1380,10 +1365,10 @@
         <v>49</v>
       </c>
       <c r="N4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="O4" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="P4" t="s">
         <v>28</v>
@@ -1436,10 +1421,10 @@
         <v>58</v>
       </c>
       <c r="N5" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="O5" t="s">
-        <v>236</v>
+        <v>54</v>
       </c>
       <c r="P5" t="s">
         <v>28</v>
@@ -1492,10 +1477,10 @@
         <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="O6" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="P6" t="s">
         <v>28</v>
@@ -1551,7 +1536,7 @@
         <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="P7" t="s">
         <v>28</v>
@@ -1604,10 +1589,10 @@
         <v>85</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="O8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="P8" t="s">
         <v>28</v>
@@ -1660,10 +1645,10 @@
         <v>95</v>
       </c>
       <c r="N9" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="O9" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="P9" t="s">
         <v>28</v>
@@ -1719,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="P10" t="s">
         <v>28</v>
@@ -1772,10 +1757,10 @@
         <v>111</v>
       </c>
       <c r="N11" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="O11" t="s">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="P11" t="s">
         <v>28</v>
@@ -1831,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="O12" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="P12" t="s">
         <v>28</v>
@@ -1884,10 +1869,10 @@
         <v>128</v>
       </c>
       <c r="N13" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O13" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="P13" t="s">
         <v>28</v>
@@ -1940,10 +1925,10 @@
         <v>137</v>
       </c>
       <c r="N14" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="O14" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="P14" t="s">
         <v>28</v>
@@ -1996,10 +1981,10 @@
         <v>147</v>
       </c>
       <c r="N15" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="O15" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="P15" t="s">
         <v>28</v>
@@ -2052,10 +2037,10 @@
         <v>156</v>
       </c>
       <c r="N16" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="O16" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P16" t="s">
         <v>28</v>
@@ -2223,7 +2208,7 @@
         <v>173</v>
       </c>
       <c r="O19" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s">
         <v>28</v>
@@ -2444,7 +2429,7 @@
         <v>189</v>
       </c>
       <c r="N23" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s">
         <v>190</v>
@@ -2500,7 +2485,7 @@
         <v>28</v>
       </c>
       <c r="N24" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s">
         <v>195</v>
@@ -2556,10 +2541,10 @@
         <v>28</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
